--- a/diseases/d240/1980-1984.xlsx
+++ b/diseases/d240/1980-1984.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">

--- a/diseases/d240/1980-1984.xlsx
+++ b/diseases/d240/1980-1984.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
